--- a/projects/回收费价目单_2026.xlsx
+++ b/projects/回收费价目单_2026.xlsx
@@ -1791,7 +1791,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="22">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>16</v>
@@ -1814,7 +1814,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="29">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D6" s="30" t="s">
         <v>16</v>
@@ -1837,7 +1837,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="36">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D7" s="37" t="s">
         <v>16</v>
@@ -1860,7 +1860,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>17</v>
@@ -1883,7 +1883,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>17</v>
@@ -1906,7 +1906,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>17</v>
@@ -1929,7 +1929,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>17</v>
@@ -1952,7 +1952,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="50">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>19</v>
@@ -1975,7 +1975,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>20</v>
@@ -1998,7 +1998,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="50">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D14" s="51" t="s">
         <v>21</v>
@@ -2021,7 +2021,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D15" s="44" t="s">
         <v>22</v>
@@ -2044,7 +2044,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>23</v>
@@ -2067,7 +2067,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>24</v>
@@ -2090,7 +2090,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>24</v>
@@ -2113,7 +2113,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="60">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D19" s="61" t="s">
         <v>24</v>

--- a/projects/回收费价目单_2026.xlsx
+++ b/projects/回收费价目单_2026.xlsx
@@ -1797,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="24">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F5" s="25">
         <v>0</v>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="31">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F6" s="32">
         <v>50</v>
@@ -1843,7 +1843,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="38">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F7" s="39">
         <v>100</v>
@@ -1866,7 +1866,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F8" s="46">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>17</v>
       </c>
       <c r="E9" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F9" s="46">
         <v>50</v>
@@ -1912,7 +1912,7 @@
         <v>17</v>
       </c>
       <c r="E10" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F10" s="46">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F11" s="46">
         <v>1000</v>
@@ -1958,7 +1958,7 @@
         <v>19</v>
       </c>
       <c r="E12" s="52">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F12" s="53">
         <v>0</v>
@@ -1981,7 +1981,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F13" s="46">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="52">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F14" s="53">
         <v>0</v>
@@ -2027,7 +2027,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F15" s="46">
         <v>0</v>
@@ -2050,7 +2050,7 @@
         <v>23</v>
       </c>
       <c r="E16" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F16" s="46">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F17" s="46">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="45">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F18" s="46">
         <v>100</v>
@@ -2119,7 +2119,7 @@
         <v>24</v>
       </c>
       <c r="E19" s="62">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="F19" s="63">
         <v>200</v>
